--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,52 +608,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>Carroll Daniel Construction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8b3e0cb0c3863c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
+          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Advisor II, Data Architect</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21bd27b152469170</t>
+          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f2e018b3b0d55e</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
+          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SolidLine Media</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8185f66fc8c270</t>
+          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Full Stack – AI Engineer (Senior Software Engineer)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Family Insurance</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c5e79cbd14d908</t>
+          <t>https://www.indeed.com/viewjob?jk=65acbad9fc6000b8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>SAP Security Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,77 +1081,77 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e89cb44acf96f0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=99f20f1d8e4ac8db</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Full Stack – AI Engineer (Senior Software Engineer)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>GreatAmerica Financial Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65acbad9fc6000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a73f224d7e2859e4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SAP Security Consultant</t>
+          <t>Full Stack Programmer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, Google Cloud Platform</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f20f1d8e4ac8db</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6b01477b638e08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Azure Data Engineer I</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GreatAmerica Financial Services</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73f224d7e2859e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Programmer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f5c62a0200f541</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8203af416f8f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
@@ -1448,25 +1448,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Engineer, Energy Intelligence (Remote, US)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, GCP, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=e972715f58cab3b7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Engineer, Energy Intelligence (Remote, US)</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, GCP, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e972715f58cab3b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30154588ed7f957f</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>SAP Application Support Trainee</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SAP Application Support Trainee</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
@@ -2288,52 +2288,52 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Visualization Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=867f580c7e3bb0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Sr. Application Development</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PENNYMAC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=4a26ae619bfe9ea5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer II 4P/554</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4P Consulting Inc.</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Hadoop, Hive, Spark, Oracle, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d963e021c819ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc1b8c72693e77a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, CRM</t>
+          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b266df7f25223b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0b570a425db53cdf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=c276ceaec78f13bf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,104 +2761,104 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
+          <t>AWS, Lambda, S3, ECS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee7df5cbe03d450</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MLOps Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4687b9b235a9a6ce</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, Scala, CI/CD, Terraform, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7929c83226ae75b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Azure Databricks Architect-3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62210abb12166a07</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb9f762b587a290</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, RDS, Azure, GCP, Spark, Snowflake, dbt</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26a71508d797185b</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-3</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb9f762b587a290</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Associate Software Engineer, Credit Tech</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=91f8471c0b8e5715</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Consultant, Data Management</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Beghou Consulting</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Snowflake, Oracle, PostgreSQL, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ad03af6a4ac792</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>Aeroflow Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Asheville, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1802cfcb8371e8</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,112 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Aeroflow Health</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Asheville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Full Stack Programmer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GreatAmerica Financial Services</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73f224d7e2859e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6b01477b638e08</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Programmer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GreatAmerica Financial Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6b01477b638e08</t>
+          <t>https://www.indeed.com/viewjob?jk=a73f224d7e2859e4</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SAP Application Support Trainee</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>SAP Application Support Trainee</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
+          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Application Development</t>
+          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PENNYMAC</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a26ae619bfe9ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=6b82db82dc8d84bf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc1b8c72693e77a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b570a425db53cdf</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b570a425db53cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=c276ceaec78f13bf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
+          <t>Sr. Application Development</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>PENNYMAC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c276ceaec78f13bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4a26ae619bfe9ea5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc1b8c72693e77a</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,69 +2831,69 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee7df5cbe03d450</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee7df5cbe03d450</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-3</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb9f762b587a290</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Azure Databricks Architect-3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb9f762b587a290</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Software Engineer, Credit Tech</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f8471c0b8e5715</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Associate Software Engineer, Credit Tech</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=91f8471c0b8e5715</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>(Remote) Fullstack Software Engineer (Special Projects Team)</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Snowflake, DynamoDB, CI/CD</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e2c56fc5827763</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
+          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
+          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
+          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Disney Entertainment Television</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
+          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Disney Entertainment Television</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
+          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
+          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Full Stack – AI Engineer (Senior Software Engineer)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65acbad9fc6000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SAP Security Consultant</t>
+          <t>Java Full Stack – AI Engineer (Senior Software Engineer)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, Google Cloud Platform</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f20f1d8e4ac8db</t>
+          <t>https://www.indeed.com/viewjob?jk=65acbad9fc6000b8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Data Engineer I</t>
+          <t>SAP Security Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=99f20f1d8e4ac8db</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Programmer</t>
+          <t>Azure Data Engineer I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6b01477b638e08</t>
+          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Full Stack Programmer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GreatAmerica Financial Services</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73f224d7e2859e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6b01477b638e08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>GreatAmerica Financial Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=a73f224d7e2859e4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Azure, GCP, Spark, Scala, MySQL, Data Modeling, Power BI, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=661c70c9e0e46642</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=12162f7263a7c160</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,684 +1651,684 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=acb104e601709bfd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer, Energy Intelligence (Remote, US)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, GCP, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e972715f58cab3b7</t>
+          <t>https://www.indeed.com/viewjob?jk=deda4bc3e265d569</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3d7781bc7369a2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=0e26027dabf08cc2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=27ebf8841ee8f534</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=f1375b18f4b3eb9d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=c692a4a08cd183d5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2f604810722be6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=d16e5236a057c830</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0862033efcd1106</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SAP Application Support Trainee</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb76a8857455140</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a25698d6c37e94a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=d143846e3e4eb595</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=533857e56d9848da</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=c3ed41e45f438a2d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=54ce9e5502eb1856</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0a6ecb46a52f03</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=9950a2ee957b024c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2337,46 +2337,46 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7604b05bdd0ea604</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b82db82dc8d84bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b570a425db53cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
+          <t>Senior Engineer, Energy Intelligence (Remote, US)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, GCP, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c276ceaec78f13bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e972715f58cab3b7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Application Development</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PENNYMAC</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a26ae619bfe9ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc1b8c72693e77a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,15 +2718,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,102 +2736,102 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
+          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>SAP Application Support Trainee</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,137 +2841,137 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee7df5cbe03d450</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-3</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb9f762b587a290</t>
+          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Software Engineer, Credit Tech</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f8471c0b8e5715</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b82db82dc8d84bf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Radwell International</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+          <t>https://www.indeed.com/viewjob?jk=0b570a425db53cdf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c276ceaec78f13bf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Sr. Application Development</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>PENNYMAC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a26ae619bfe9ea5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc1b8c72693e77a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,15 +3453,15 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,15 +3488,15 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,15 +3523,15 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,15 +3558,15 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,94 +3576,94 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee7df5cbe03d450</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,17 +3741,787 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II (Remote)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Azure Databricks Architect-3</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Mahwah, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aeb9f762b587a290</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>YUM! Brands, Inc.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Developer (Go / Backend Engineering)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SPAN Enterprises, LLC</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>A. Duie Pyle, INC.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>West Chester, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer, Credit Tech</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91f8471c0b8e5715</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Radwell International</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Willingboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>University of Texas Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Tango</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,12 +783,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Disney Entertainment Television</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Disney Entertainment Television</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
+          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Programmer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GreatAmerica Financial Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Google Cloud Platform, GCP, YARN, Scala, PostgreSQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6b01477b638e08</t>
+          <t>https://www.indeed.com/viewjob?jk=a73f224d7e2859e4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GreatAmerica Financial Services</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73f224d7e2859e4</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>SRS Distribution</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Spark, Scala, MySQL, Data Modeling, Power BI, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
+          <t>https://www.indeed.com/viewjob?jk=661c70c9e0e46642</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, MySQL, Data Modeling, Power BI, Splunk, Jenkins</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=661c70c9e0e46642</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer III, Platform Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>Herbalife</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=12162f7263a7c160</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12162f7263a7c160</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,624 +1711,624 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb104e601709bfd</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ramsey Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deda4bc3e265d569</t>
+          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Engineer, Energy Intelligence (Remote, US)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, RDS, GCP, Scala, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3d7781bc7369a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e972715f58cab3b7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e26027dabf08cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ebf8841ee8f534</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1375b18f4b3eb9d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c692a4a08cd183d5</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f604810722be6</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d16e5236a057c830</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0862033efcd1106</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb76a8857455140</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a25698d6c37e94a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>SAP Application Support Trainee</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d143846e3e4eb595</t>
+          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533857e56d9848da</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ed41e45f438a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ce9e5502eb1856</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0a6ecb46a52f03</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9950a2ee957b024c</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2337,46 +2337,46 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7604b05bdd0ea604</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,102 +2421,102 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Application Development</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>PENNYMAC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a26ae619bfe9ea5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc1b8c72693e77a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer, Energy Intelligence (Remote, US)</t>
+          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, GCP, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e972715f58cab3b7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b82db82dc8d84bf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=0b570a425db53cdf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=c276ceaec78f13bf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,54 +2631,54 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,137 +2701,137 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a077c257a4cf0b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee7df5cbe03d450</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SAP Application Support Trainee</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer - II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
+          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer Sr - Microservices/Kafka/ETL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Kafka, Oracle, ETL, Jenkins, Docker, Jenkins, Git, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=3673ee144fef09b1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Associate Software Engineer, Credit Tech</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=91f8471c0b8e5715</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Azure Databricks Architect-3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb9f762b587a290</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acf3efd34722f19</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b82db82dc8d84bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b570a425db53cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c276ceaec78f13bf</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Application Development</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PENNYMAC</t>
+          <t>Radwell International</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,1197 +3331,42 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a26ae619bfe9ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc1b8c72693e77a</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Data Operations Developer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Geotab</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Nation's Best Sports</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Solutions Engineer II - Networking</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b11bc9d20fc1e2e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Solutions Engineer II - Networking</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a6f623279ee6d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Solutions Engineer II - Networking</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3cccca60e879db</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Solutions Engineer II - Networking</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f821dc8a5f6559</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Product Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Sifted</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee7df5cbe03d450</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>TESSCO</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Hunt Valley, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Finance of America</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Burrell Behavioral Health</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II (Remote)</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Azure Databricks Architect-3</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Mahwah, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb9f762b587a290</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>YUM! Brands, Inc.</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>SPAN Enterprises, LLC</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>A. Duie Pyle, INC.</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>West Chester, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer, Credit Tech</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91f8471c0b8e5715</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Radwell International</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>MeridianLink</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Tango</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>MeridianLink</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=503269b060f28151</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbeb792ea58b7a87</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd899ffea8f1b74c</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f22565dd904e0808</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8fcbfbc5352b0bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1da94812ec374b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5cdada52faf29e</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5676e61db2aa81f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de6aa6e4975245c5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,12 +783,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Disney Entertainment Television</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
+          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Disney Entertainment Television</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Application Developer III, Platform Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Herbalife</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116acc2ab05b269d</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=12162f7263a7c160</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12162f7263a7c160</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ramsey Solutions</t>
+          <t>Radiant Digital</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba46b1aa50f7279f</t>
+          <t>https://www.indeed.com/viewjob?jk=21b7e73d33f00e62</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer, Energy Intelligence (Remote, US)</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, RDS, GCP, Scala, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e972715f58cab3b7</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>SAP Application Support Trainee</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SAP Application Support Trainee</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Senior Machine Learning Engineer, Shield</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Box</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=88492e295288a867</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Data Engineering Java/Python</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Sr. Application Development</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PENNYMAC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=4a26ae619bfe9ea5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Application Development</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PENNYMAC</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a26ae619bfe9ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc1b8c72693e77a</t>
+          <t>https://www.indeed.com/viewjob?jk=ada1c920f207c639</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b82db82dc8d84bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc1b8c72693e77a</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b570a425db53cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=6b82db82dc8d84bf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c276ceaec78f13bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,69 +2691,69 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee7df5cbe03d450</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee7df5cbe03d450</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer - II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - II</t>
+          <t>Machine Learning Engineer II (Remote)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II (Remote)</t>
+          <t>Azure Databricks Architect-3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
+          <t>https://www.indeed.com/viewjob?jk=aeb9f762b587a290</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer Sr - Microservices/Kafka/ETL</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Kafka, Oracle, ETL, Jenkins, Docker, Jenkins, Git, Bitbucket, Python</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3673ee144fef09b1</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Software Engineer, Credit Tech</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Morningstar</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f8471c0b8e5715</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-3</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb9f762b587a290</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer Sr - Microservices/Kafka/ETL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>RDS, Kafka, Oracle, ETL, Jenkins, Docker, Jenkins, Git, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=3673ee144fef09b1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Associate Software Engineer, Credit Tech</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>Morningstar</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=91f8471c0b8e5715</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,19 +3156,19 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,77 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Enterprise AI Architect</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Radwell International</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Willingboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, NoSQL, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=291c96af0e7cea02</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)</t>
+          <t>DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Carroll Daniel Construction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9cf410db691568</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8b3e0cb0c3863c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DATA ARCHITECT</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carroll Daniel Construction</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8b3e0cb0c3863c</t>
+          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Data Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
+          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Disney Entertainment Television</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
+          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Disney Entertainment Television</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
+          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
+          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,77 +1011,77 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Full Stack – AI Engineer (Senior Software Engineer)</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,102 +1091,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65acbad9fc6000b8</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SAP Security Consultant</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Azure, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f20f1d8e4ac8db</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GreatAmerica Financial Services</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, Scala, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73f224d7e2859e4</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SRS Distribution</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fcb451d7086751</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, MySQL, Data Modeling, Power BI, Splunk, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=661c70c9e0e46642</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST III</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12162f7263a7c160</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,207 +1616,207 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Radiant Digital</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b7e73d33f00e62</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,242 +1931,242 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64eeda5b2dfcfe99</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SAP Application Support Trainee</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e8e9db0adaeff1</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8a7818486ff2d</t>
+          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Shield</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88492e295288a867</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer - II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Engineering Java/Python</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL, Splunk, CI/CD</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ec8999487afb4f6</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Application Development</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PENNYMAC</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a26ae619bfe9ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ada1c920f207c639</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc1b8c72693e77a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Global Data Analytics for Internal Audit Function - AMS</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, MapReduce, Scala, Snowflake, Dimensional Modeling, ETL</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,742 +2561,42 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b82db82dc8d84bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Data Operations Developer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Geotab</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Product Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Sifted</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee7df5cbe03d450</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>TESSCO</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Hunt Valley, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Finance of America</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Burrell Behavioral Health</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Data Engineer - II</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>CINC</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer II (Remote)</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, CI/CD, Git, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd0ef78a415d3113</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Azure Databricks Architect-3</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Mahwah, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aeb9f762b587a290</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>YUM! Brands, Inc.</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>SPAN Enterprises, LLC</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>A. Duie Pyle, INC.</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>West Chester, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Software Engineer Sr - Microservices/Kafka/ETL</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Kafka, Oracle, ETL, Jenkins, Docker, Jenkins, Git, Bitbucket, Python</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3673ee144fef09b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer, Credit Tech</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, NoSQL, Git</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91f8471c0b8e5715</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58638a1a93a5925c</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>MeridianLink</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Remote)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Tango</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>MeridianLink</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>Software Engineer III - Fullstack with AWS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,52 +1081,52 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,69 +1851,69 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - II</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer - II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,15 +2586,85 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>YUM! Brands, Inc.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>University of Texas Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Data Engineer I</t>
+          <t>Software Engineer III - Fullstack with AWS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Premise Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ELT, Talend</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=353cdf1ee00c6fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack with AWS</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,69 +1081,69 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,69 +1886,69 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,77 +2201,77 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - II</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Data Engineer - II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Sr. Software Engineer - CMG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>i2c Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=14c6d6e2d1865fce</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,157 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tango</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>University of Texas Health Science Center at San Antonio</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>YUM! Brands, Inc.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote in CA)</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05ccb57abd2eb2be</t>
+          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Disney Entertainment Television</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
+          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Disney Entertainment Television</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
+          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
+          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
+          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
+          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fairview Health Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,77 +976,77 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Fullstack with AWS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack with AWS</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
@@ -1238,25 +1238,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
@@ -1448,25 +1448,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Machine Learning Engineer (171679)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,69 +1886,69 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
         </is>
       </c>
     </row>
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Data Engineer - II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - II</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>Sakuu Corp</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=43351bc15987c6d7</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,60 +958,60 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Fullstack with AWS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fairview Health Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, MapReduce, HBase, Oozie, Spark, Kafka, Oracle</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d7b87445d04d0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack with AWS</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57d55c8e2a74923</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Agentic AI Solutions Architect - Remote, Latin America</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Step Functions, RDS, Azure, GCP, BigQuery, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=685a2624d1d330a2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=44433f5b77f36c69</t>
         </is>
       </c>
     </row>
@@ -1868,52 +1868,52 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer (171679)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b373595b350ec3d</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
         </is>
       </c>
     </row>
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Operations Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>Geotab</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer - II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, MS Excel, Python</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8846493996e830</t>
+          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Sr. Software Engineer - CMG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>i2c Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=14c6d6e2d1865fce</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - II</t>
+          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>Sakuu Corp</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
+          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
+          <t>https://www.indeed.com/viewjob?jk=43351bc15987c6d7</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - CMG</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>i2c Inc</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c6d6e2d1865fce</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sakuu Corp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43351bc15987c6d7</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,77 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>MeridianLink</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>YUM! Brands, Inc.</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Disney Entertainment Television</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, RDS, Databricks, BigQuery, Vertex AI, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06c7525b9f402e34</t>
+          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
+          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,174 +836,174 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Software Engineer III - Fullstack with AWS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
+          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b02b46801c7f10</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef8a3d8ad1cf49b7</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack with AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Agentic AI Solutions Architect - Remote, Latin America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Step Functions, RDS, Azure, GCP, BigQuery, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=685a2624d1d330a2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Agentic AI Solutions Architect - Remote, Latin America</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, RDS, Azure, GCP, BigQuery, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685a2624d1d330a2</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>The Friedkin Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=44433f5b77f36c69</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44433f5b77f36c69</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,77 +1781,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,77 +2131,77 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Operations Developer</t>
+          <t>Data Engineer - II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Geotab</t>
+          <t>CINC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2232,11 +2232,11 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd3315942275dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Sr. Software Engineer - CMG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>i2c Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=14c6d6e2d1865fce</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Sakuu Corp</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=43351bc15987c6d7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer - II</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - CMG</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>i2c Inc</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c6d6e2d1865fce</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sakuu Corp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43351bc15987c6d7</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2630,111 +2630,6 @@
         </is>
       </c>
       <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>MeridianLink</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>YUM! Brands, Inc.</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack with AWS</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Software Engineer III - Fullstack with AWS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,112 +1291,112 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Agentic AI Solutions Architect - Remote, Latin America</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, RDS, Azure, GCP, BigQuery, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685a2624d1d330a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Friedkin Group</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Dataflow, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ede0f34ce25b71</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44433f5b77f36c69</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6a5e86c2af0d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cvent</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tysons Corner, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, HBase, Scala, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131e73fa50f53df2</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - II</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CINC</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, ECS, Scala, Kafka, DynamoDB, ETL, ELT, CI/CD</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32c97e76b6269664</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - CMG</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>i2c Inc</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c6d6e2d1865fce</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sakuu Corp</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43351bc15987c6d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>Tango</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,19 +2421,19 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>University of Texas Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Sakuu Corp</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,112 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>MeridianLink</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>YUM! Brands, Inc.</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=43351bc15987c6d7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,69 +1396,69 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer (HPC/AI &amp; Distributed Systems)</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dce54831329652c4</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc8599dc51df5400</t>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>University of Texas Health Science Center at San Antonio</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, ETL, Tableau, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fff225f154716cc</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sakuu Corp</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,15 +2516,225 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Developer (Go / Backend Engineering)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SPAN Enterprises, LLC</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tango</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>YUM! Brands, Inc.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Salesforce Solution Architect</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Coresphere</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sakuu Corp</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=43351bc15987c6d7</t>
         </is>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Torq</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, BigQuery, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9f68666dbb80cd</t>
+          <t>https://www.indeed.com/viewjob?jk=1c1ca4fadb364b85</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Solution Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)-1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Associated Wholesale Grocers</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,209 +521,209 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4780af39e79827</t>
+          <t>https://www.indeed.com/viewjob?jk=00b0ecbc06d206c1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-1</t>
+          <t>DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Carroll Daniel Construction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00b0ecbc06d206c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8b3e0cb0c3863c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DATA ARCHITECT</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carroll Daniel Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8b3e0cb0c3863c</t>
+          <t>https://www.indeed.com/viewjob?jk=68c4aadfa37313dc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86e480fe3755cd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior IAM Integration Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
+          <t>https://www.indeed.com/viewjob?jk=6b82fbb2e1ad7212</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
+          <t>Senior IAM Integration Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e466f53edec490</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
+          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
+          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,54 +811,54 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1052fb6437c3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Blockchain Java Backend Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
+          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack with AWS</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=341544bd6730c9ac</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,38 +972,38 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,174 +1851,174 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,234 +2141,234 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=66f180565bedb48a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Burrell Behavioral Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sakuu Corp</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,182 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43351bc15987c6d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Developer (Go / Backend Engineering)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SPAN Enterprises, LLC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Tango</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Salesforce Solution Architect</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Coresphere</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,95 +923,95 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341544bd6730c9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=341544bd6730c9ac</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,38 +1042,38 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=663f555c3c3a4323</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9c050714c83922</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,77 +1501,77 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,209 +1676,209 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,209 +1991,209 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Software Eng/Developer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,29 +2236,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f180565bedb48a</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Burrell Behavioral Health</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ff4ba7951fc9c97</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,234 +2456,234 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Java Full Stack Engineer - Associate</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, PostgreSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=473e4f2e4cfe64c5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=66f180565bedb48a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,332 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>A. Duie Pyle, INC.</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>West Chester, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Software Developer (Go / Backend Engineering)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SPAN Enterprises, LLC</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tango</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Salesforce Solution Architect</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Coresphere</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>YUM! Brands, Inc.</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
+          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,24 +906,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,29 +946,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Intermediate Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Progressive</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Cloud Storage, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a97f6710d73548</t>
+          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663f555c3c3a4323</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9c050714c83922</t>
+          <t>https://www.indeed.com/viewjob?jk=663f555c3c3a4323</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9c050714c83922</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer with AI &amp; Kubernetes</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, Scala, Power BI, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5df4e674559910e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b7f8d62e370d21c</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,42 +1826,42 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,69 +2131,69 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Eng/Developer III</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Eng/Developer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Remote)</t>
+          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tango</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Git</t>
+          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d66e27cb89a5630</t>
+          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
+          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
+          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,24 +906,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -946,29 +946,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341544bd6730c9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e643c6d74eb444</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,69 +1046,69 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=341544bd6730c9ac</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Intermediate Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Progressive</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, ETL, ELT, dbt, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b465e27586b38fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2845c99fbf7bb445</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,52 +1606,52 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Snowflake SME</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74494a10316e7fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,29 +2096,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2127,38 +2127,38 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Eng/Developer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Eng/Developer III</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,50 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Salesforce Solution Architect</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Coresphere</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45366327b45aca00</t>
+          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
+          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
+          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Engineer</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48f5c60379802d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,104 +906,104 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e643c6d74eb444</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=341544bd6730c9ac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e643c6d74eb444</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341544bd6730c9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,139 +1186,139 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54fbc1b6f53ddcb1</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=663f555c3c3a4323</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9c050714c83922</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663f555c3c3a4323</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9c050714c83922</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer with AI &amp; Kubernetes</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hudson Manpower</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3d2714f39bd085</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Sr. Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,77 +1676,77 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snowflake SME</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccefe385c15cc707</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Eng/Developer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,59 +2071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Eng/Developer III</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,29 +2201,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Nation's Best Sports</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Java Full Stack Engineer - Associate</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, PostgreSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=473e4f2e4cfe64c5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=66f180565bedb48a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Associate</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, PostgreSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473e4f2e4cfe64c5</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f180565bedb48a</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer - CICD</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4cd3477fb442eb3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Software Developer (Go / Backend Engineering)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>SPAN Enterprises, LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>YUM! Brands, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-Stack Software Development Engineer II ( Java and Angular)</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bef7280137d41c</t>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Machine Learning Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,87 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Azure, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>BI Reporting Developer I</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Salesforce Solution Architect</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Coresphere</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=196dc3bc7f2912cf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
+          <t>Sr. Databricks Architect &amp; Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Des Moines, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Databricks, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
+          <t>https://www.indeed.com/viewjob?jk=13cef02d1e7cd394</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
+          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Wellmark Blue Cross and Blue Shield</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
+          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,24 +871,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -911,64 +911,64 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e643c6d74eb444</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341544bd6730c9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e643c6d74eb444</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,77 +1011,77 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=341544bd6730c9ac</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>MLops Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Velvetech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Software Engineer III - Fullstack with AWS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,94 +1231,94 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663f555c3c3a4323</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9c050714c83922</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=663f555c3c3a4323</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9c050714c83922</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Developer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ac4966435dab5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,139 +1676,139 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Agentic AI Solutions Architect - Remote, Latin America</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>Bluelight Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>AWS, Glue, Step Functions, RDS, Azure, GCP, BigQuery, Snowflake, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=685a2624d1d330a2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Reef Capital Partners</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=44433f5b77f36c69</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,77 +1991,77 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Eng/Developer III</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Eng/Developer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>Ripplehire</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nation's Best Sports</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, SQL Server, MySQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4021abb69b19b3ac</t>
+          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Associate</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, PostgreSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473e4f2e4cfe64c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f180565bedb48a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Java Full Stack Engineer - Associate</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, PostgreSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=473e4f2e4cfe64c5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=66f180565bedb48a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer - CICD</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=f4cd3477fb442eb3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - CICD</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4cd3477fb442eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SPAN Enterprises, LLC</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A. Duie Pyle, INC.</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>YUM! Brands, Inc.</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f545aa447f1c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BI Reporting Developer I</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>A. Duie Pyle, INC.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Machine Learning Software Engineer</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,157 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Developer (Go / Backend Engineering)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SPAN Enterprises, LLC</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BI Reporting Developer I</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ECS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Machine Learning Software Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>AWS, Azure, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=196dc3bc7f2912cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Sakuu Corp</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43351bc15987c6d7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-27.xlsx
+++ b/results/job_matches_2026-02-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,70 +503,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-1</t>
+          <t>DATA ARCHITECT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Carroll Daniel Construction</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00b0ecbc06d206c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8b3e0cb0c3863c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DATA ARCHITECT</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carroll Daniel Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8b3e0cb0c3863c</t>
+          <t>https://www.indeed.com/viewjob?jk=68c4aadfa37313dc</t>
         </is>
       </c>
     </row>
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c4aadfa37313dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86e480fe3755cd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior IAM Integration Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86e480fe3755cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6b82fbb2e1ad7212</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior IAM Integration Engineer</t>
+          <t>Databricks Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OZ Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b82fbb2e1ad7212</t>
+          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior IAM Integration Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e466f53edec490</t>
+          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Sr. Databricks Architect &amp; Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Des Moines, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,104 +731,104 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Databricks, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=13cef02d1e7cd394</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Databricks Architect &amp; Developer</t>
+          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Des Moines, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Databricks, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cef02d1e7cd394</t>
+          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Digital Services Software Engineer #1741</t>
+          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Azure, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef36d6b0df82b802</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Snowflake &amp; dbt)</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d715fc100593a</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, SQL, AWS) - Navigator Platform</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,112 +871,112 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4d5c76dd819896</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Senior Quality Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=a424e0d64dae1bfe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Cleerly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e643c6d74eb444</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, Azure, Google Cloud Platform, Vertex AI</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341544bd6730c9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MLops Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Velvetech</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, Scala, SQL Server, PostgreSQL, MongoDB, MLOps</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55830710a153dc5e</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack with AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Brown &amp; Brown Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d52a4ac4cf61b3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,94 +1231,94 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Spark, Scala, Azure Cosmos DB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58bf629817888436</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=663f555c3c3a4323</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9c050714c83922</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,129 +1686,129 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Agentic AI Solutions Architect - Remote, Latin America</t>
+          <t>Data Analytics (Web and Advertising Analytics)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Extractable</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, RDS, Azure, GCP, BigQuery, Snowflake, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685a2624d1d330a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Reef Capital Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Snowflake, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e695ed23053b341</t>
+          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Machine Learning &amp; Artificial Intelligence (ML &amp; AI)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Michael Silver &amp; Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, MLflow, CI/CD, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d7c1193c8f42bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, GCP, Vertex AI, Scala</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=244a4415e537c51d</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44433f5b77f36c69</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,77 +1991,77 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Michael Silver &amp; Company</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, Power BI</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d034328689acf94</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Software Eng/Developer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f37da5c13bf79660</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Eng/Developer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Spark, Kafka, Oracle, ETL, CI/CD</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955a036d4b1cf07e</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ripplehire</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, ETL, ELT, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12fb3b1bcde35e2</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=defb7c286d56b171</t>
+          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior Software Engineer, Member AI Features</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer - Associate</t>
+          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Cloud Storage, Scala, PostgreSQL, ETL, CI/CD, Jenkins, Kubernetes</t>
+          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473e4f2e4cfe64c5</t>
+          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f180565bedb48a</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707ae926dfb9261b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - CICD</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4cd3477fb442eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,402 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Coraopolis, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Galesburg, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>A. Duie Pyle, INC.</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>West Chester, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, CloudWatch, Python</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df95271c65edaa7c</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer 2 – Full Stack (React.js, Java Spring Boot)</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Azure, GCP, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Docker, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33f233bcd06b05ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Software Developer (Go / Backend Engineering)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>SPAN Enterprises, LLC</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a80a72289b50e8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>BI Reporting Developer I</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Machine Learning Software Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=196dc3bc7f2912cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Full-Stack Software Engineer, Manufacturing/R&amp;D Data Platform (NestJS, Next.js, Kafka)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Sakuu Corp</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43351bc15987c6d7</t>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>
